--- a/diseases/d025/2000-2004.xlsx
+++ b/diseases/d025/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>40</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.7727674434621603</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>13</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>4.621729237770193</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>15</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.3340112276760813</v>
       </c>
@@ -2397,9 +2388,6 @@
       <c r="O11" t="n">
         <v>47</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.9080017460680385</v>
       </c>
@@ -2941,9 +2929,6 @@
       <c r="O14" t="n">
         <v>21</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.4676157187465137</v>
       </c>
@@ -3485,9 +3470,6 @@
       <c r="O17" t="n">
         <v>50</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.9659593043277006</v>
       </c>
@@ -4029,9 +4011,6 @@
       <c r="O20" t="n">
         <v>23</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.5121505491033246</v>
       </c>
@@ -4573,9 +4552,6 @@
       <c r="O23" t="n">
         <v>39</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.7534482573756064</v>
       </c>
@@ -5117,9 +5093,6 @@
       <c r="O26" t="n">
         <v>14</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.3117438124976759</v>
       </c>
@@ -5661,9 +5634,6 @@
       <c r="O29" t="n">
         <v>39</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.7534482573756064</v>
       </c>
@@ -6205,9 +6175,6 @@
       <c r="O32" t="n">
         <v>18</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.4008134732112975</v>
       </c>
@@ -6749,9 +6716,6 @@
       <c r="O35" t="n">
         <v>48</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.9273209321545925</v>
       </c>
@@ -7293,9 +7257,6 @@
       <c r="O38" t="n">
         <v>22</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.4898831339249192</v>
       </c>
@@ -7837,9 +7798,6 @@
       <c r="O41" t="n">
         <v>51</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.9852784904142545</v>
       </c>
@@ -8381,9 +8339,6 @@
       <c r="O44" t="n">
         <v>18</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.4008134732112975</v>
       </c>
@@ -8925,9 +8880,6 @@
       <c r="O47" t="n">
         <v>57</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>1.101193606933579</v>
       </c>
@@ -9469,9 +9421,6 @@
       <c r="O50" t="n">
         <v>27</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.6012202098169462</v>
       </c>
@@ -10013,9 +9962,6 @@
       <c r="O53" t="n">
         <v>47</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.9080017460680385</v>
       </c>
@@ -10557,9 +10503,6 @@
       <c r="O56" t="n">
         <v>21</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.4676157187465137</v>
       </c>
@@ -11101,9 +11044,6 @@
       <c r="O59" t="n">
         <v>49</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.9466401182411465</v>
       </c>
@@ -11645,9 +11585,6 @@
       <c r="O62" t="n">
         <v>19</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.4230808883897029</v>
       </c>
@@ -12189,9 +12126,6 @@
       <c r="O65" t="n">
         <v>41</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.7920866295487144</v>
       </c>
@@ -12733,9 +12667,6 @@
       <c r="O68" t="n">
         <v>23</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.5121505491033246</v>
       </c>
@@ -13277,9 +13208,6 @@
       <c r="O71" t="n">
         <v>37</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.7148098852024984</v>
       </c>
@@ -13821,9 +13749,6 @@
       <c r="O74" t="n">
         <v>20</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.4453483035681083</v>
       </c>
@@ -14513,9 +14438,6 @@
       <c r="O78" t="n">
         <v>41</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.7902896912877886</v>
       </c>
@@ -15057,9 +14979,6 @@
       <c r="O81" t="n">
         <v>13</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>4.560563404986801</v>
       </c>
@@ -15453,9 +15372,6 @@
       <c r="O83" t="n">
         <v>26</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.5760295919694386</v>
       </c>
@@ -16145,9 +16061,6 @@
       <c r="O87" t="n">
         <v>37</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.7131882579914189</v>
       </c>
@@ -16689,9 +16602,6 @@
       <c r="O90" t="n">
         <v>23</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.5095646390498879</v>
       </c>
@@ -17381,9 +17291,6 @@
       <c r="O94" t="n">
         <v>53</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>1.021593991176897</v>
       </c>
@@ -17925,9 +17832,6 @@
       <c r="O97" t="n">
         <v>21</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.4652546704368542</v>
       </c>
@@ -18617,9 +18521,6 @@
       <c r="O101" t="n">
         <v>42</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.8095650496118811</v>
       </c>
@@ -19161,9 +19062,6 @@
       <c r="O104" t="n">
         <v>22</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.4874096547433711</v>
       </c>
@@ -19853,9 +19751,6 @@
       <c r="O108" t="n">
         <v>45</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.8673911245841582</v>
       </c>
@@ -20397,9 +20292,6 @@
       <c r="O111" t="n">
         <v>27</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.5981845762759553</v>
       </c>
@@ -21089,9 +20981,6 @@
       <c r="O115" t="n">
         <v>45</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.8673911245841582</v>
       </c>
@@ -21633,9 +21522,6 @@
       <c r="O118" t="n">
         <v>26</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.5760295919694386</v>
       </c>
@@ -22325,9 +22211,6 @@
       <c r="O122" t="n">
         <v>52</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>1.002318632852805</v>
       </c>
@@ -22869,9 +22752,6 @@
       <c r="O125" t="n">
         <v>18</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.3987897175173036</v>
       </c>
@@ -23561,9 +23441,6 @@
       <c r="O129" t="n">
         <v>27</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.5204346747504949</v>
       </c>
@@ -24105,9 +23982,6 @@
       <c r="O132" t="n">
         <v>27</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.5981845762759553</v>
       </c>
@@ -24797,9 +24671,6 @@
       <c r="O136" t="n">
         <v>40</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.7710143329636963</v>
       </c>
@@ -25341,9 +25212,6 @@
       <c r="O139" t="n">
         <v>16</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.3544797489042699</v>
       </c>
@@ -26033,9 +25901,6 @@
       <c r="O143" t="n">
         <v>47</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.905941841232343</v>
       </c>
@@ -26577,9 +26442,6 @@
       <c r="O146" t="n">
         <v>26</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.5760295919694386</v>
       </c>
@@ -27269,9 +27131,6 @@
       <c r="O150" t="n">
         <v>38</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.7324636163155114</v>
       </c>
@@ -27813,9 +27672,6 @@
       <c r="O153" t="n">
         <v>23</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.5095646390498879</v>
       </c>
@@ -28505,9 +28361,6 @@
       <c r="O157" t="n">
         <v>33</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.6360868246950494</v>
       </c>
@@ -29049,9 +28902,6 @@
       <c r="O160" t="n">
         <v>22</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.4874096547433711</v>
       </c>
@@ -29741,9 +29591,6 @@
       <c r="O164" t="n">
         <v>37</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.7114637578438879</v>
       </c>
@@ -30285,9 +30132,6 @@
       <c r="O167" t="n">
         <v>8</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>2.781573466570702</v>
       </c>
@@ -30681,9 +30525,6 @@
       <c r="O169" t="n">
         <v>22</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.4847935682878017</v>
       </c>
@@ -31373,9 +31214,6 @@
       <c r="O173" t="n">
         <v>47</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.9037512599638576</v>
       </c>
@@ -31917,9 +31755,6 @@
       <c r="O176" t="n">
         <v>23</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.5068296395736108</v>
       </c>
@@ -32609,9 +32444,6 @@
       <c r="O180" t="n">
         <v>34</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.6537775072078971</v>
       </c>
@@ -33153,9 +32985,6 @@
       <c r="O183" t="n">
         <v>17</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.3746132118587558</v>
       </c>
@@ -33845,9 +33674,6 @@
       <c r="O187" t="n">
         <v>46</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0.8845225097518606</v>
       </c>
@@ -34389,9 +34215,6 @@
       <c r="O190" t="n">
         <v>21</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.4627574970019925</v>
       </c>
@@ -35081,9 +34904,6 @@
       <c r="O194" t="n">
         <v>45</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.8652937595398636</v>
       </c>
@@ -35625,9 +35445,6 @@
       <c r="O197" t="n">
         <v>31</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.6831182098600842</v>
       </c>
@@ -36317,9 +36134,6 @@
       <c r="O201" t="n">
         <v>43</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.8268362591158698</v>
       </c>
@@ -36861,9 +36675,6 @@
       <c r="O204" t="n">
         <v>22</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.4847935682878017</v>
       </c>
@@ -37553,9 +37364,6 @@
       <c r="O208" t="n">
         <v>32</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.6153200067839031</v>
       </c>
@@ -38097,9 +37905,6 @@
       <c r="O211" t="n">
         <v>15</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.3305410692871375</v>
       </c>
@@ -38789,9 +38594,6 @@
       <c r="O215" t="n">
         <v>38</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.7306925080558849</v>
       </c>
@@ -39333,9 +39135,6 @@
       <c r="O218" t="n">
         <v>19</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.4186853544303741</v>
       </c>
@@ -40025,9 +39824,6 @@
       <c r="O222" t="n">
         <v>45</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.8652937595398636</v>
       </c>
@@ -40569,9 +40365,6 @@
       <c r="O225" t="n">
         <v>18</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.396649283144565</v>
       </c>
@@ -41261,9 +41054,6 @@
       <c r="O229" t="n">
         <v>46</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0.8845225097518606</v>
       </c>
@@ -41805,9 +41595,6 @@
       <c r="O232" t="n">
         <v>27</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.5949739247168475</v>
       </c>
@@ -42497,9 +42284,6 @@
       <c r="O236" t="n">
         <v>34</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.6537775072078971</v>
       </c>
@@ -43041,9 +42825,6 @@
       <c r="O239" t="n">
         <v>24</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.52886571085942</v>
       </c>
@@ -43733,9 +43514,6 @@
       <c r="O243" t="n">
         <v>30</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.5768625063599091</v>
       </c>
@@ -44277,9 +44055,6 @@
       <c r="O246" t="n">
         <v>14</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.3085049980013284</v>
       </c>
@@ -44969,9 +44744,6 @@
       <c r="O250" t="n">
         <v>39</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.7481361339202046</v>
       </c>
@@ -45513,9 +45285,6 @@
       <c r="O253" t="n">
         <v>5</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>1.726489528841007</v>
       </c>
@@ -45909,9 +45678,6 @@
       <c r="O255" t="n">
         <v>17</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.3724256895735485</v>
       </c>
@@ -46601,9 +46367,6 @@
       <c r="O259" t="n">
         <v>39</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0.7481361339202046</v>
       </c>
@@ -47145,9 +46908,6 @@
       <c r="O262" t="n">
         <v>32</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.7010365921384443</v>
       </c>
@@ -47837,9 +47597,6 @@
       <c r="O266" t="n">
         <v>36</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.6905872005417273</v>
       </c>
@@ -48381,9 +48138,6 @@
       <c r="O269" t="n">
         <v>39</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.8543883466687288</v>
       </c>
@@ -49073,9 +48827,6 @@
       <c r="O273" t="n">
         <v>43</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0.8248680450915076</v>
       </c>
@@ -49617,9 +49368,6 @@
       <c r="O276" t="n">
         <v>30</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.6572218051297914</v>
       </c>
@@ -50309,9 +50057,6 @@
       <c r="O280" t="n">
         <v>36</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0.6905872005417273</v>
       </c>
@@ -50853,9 +50598,6 @@
       <c r="O283" t="n">
         <v>33</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0.7229439856427706</v>
       </c>
@@ -51545,9 +51287,6 @@
       <c r="O287" t="n">
         <v>32</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0.6138552893704243</v>
       </c>
@@ -52089,9 +51828,6 @@
       <c r="O290" t="n">
         <v>35</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0.7667587726514233</v>
       </c>
@@ -52781,9 +52517,6 @@
       <c r="O294" t="n">
         <v>40</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0.7673191117130302</v>
       </c>
@@ -53325,9 +53058,6 @@
       <c r="O297" t="n">
         <v>25</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0.5476848376081596</v>
       </c>
@@ -54017,9 +53747,6 @@
       <c r="O301" t="n">
         <v>25</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0.479574444820644</v>
       </c>
@@ -54561,9 +54288,6 @@
       <c r="O304" t="n">
         <v>22</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0.4819626570951804</v>
       </c>
@@ -55253,9 +54977,6 @@
       <c r="O308" t="n">
         <v>34</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0.6522212449560758</v>
       </c>
@@ -55797,9 +55518,6 @@
       <c r="O311" t="n">
         <v>27</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0.5914996246168123</v>
       </c>
@@ -56489,9 +56207,6 @@
       <c r="O315" t="n">
         <v>33</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0.6330382671632501</v>
       </c>
@@ -57033,9 +56748,6 @@
       <c r="O318" t="n">
         <v>32</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0.7010365921384443</v>
       </c>
@@ -57725,9 +57437,6 @@
       <c r="O322" t="n">
         <v>35</v>
       </c>
-      <c r="Q322" t="n">
-        <v>0</v>
-      </c>
       <c r="R322" t="n">
         <v>0.6714042227489015</v>
       </c>
@@ -58269,9 +57978,6 @@
       <c r="O325" t="n">
         <v>22</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0.4819626570951804</v>
       </c>
@@ -58961,9 +58667,6 @@
       <c r="O329" t="n">
         <v>25</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0.479574444820644</v>
       </c>
@@ -59505,9 +59208,6 @@
       <c r="O332" t="n">
         <v>28</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>0.6134070181211387</v>
       </c>
@@ -60197,9 +59897,6 @@
       <c r="O336" t="n">
         <v>22</v>
       </c>
-      <c r="Q336" t="n">
-        <v>0</v>
-      </c>
       <c r="R336" t="n">
         <v>0.4207991051515756</v>
       </c>
@@ -60741,9 +60438,6 @@
       <c r="O339" t="n">
         <v>13</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>4.449487196600591</v>
       </c>
@@ -61137,9 +60831,6 @@
       <c r="O341" t="n">
         <v>23</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>0.5008991684529348</v>
       </c>
@@ -61829,9 +61520,6 @@
       <c r="O345" t="n">
         <v>29</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0.5546897295179861</v>
       </c>
@@ -62373,9 +62061,6 @@
       <c r="O348" t="n">
         <v>21</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0.4573427190222448</v>
       </c>
@@ -63065,9 +62750,6 @@
       <c r="O352" t="n">
         <v>31</v>
       </c>
-      <c r="Q352" t="n">
-        <v>0</v>
-      </c>
       <c r="R352" t="n">
         <v>0.5929441936226748</v>
       </c>
@@ -63609,9 +63291,6 @@
       <c r="O355" t="n">
         <v>28</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0.6097902920296598</v>
       </c>
@@ -64301,9 +63980,6 @@
       <c r="O359" t="n">
         <v>29</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>0.5546897295179861</v>
       </c>
@@ -64845,9 +64521,6 @@
       <c r="O362" t="n">
         <v>27</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0.5880120673143148</v>
       </c>
@@ -65537,9 +65210,6 @@
       <c r="O366" t="n">
         <v>25</v>
       </c>
-      <c r="Q366" t="n">
-        <v>0</v>
-      </c>
       <c r="R366" t="n">
         <v>0.4781808013086087</v>
       </c>
@@ -66081,9 +65751,6 @@
       <c r="O369" t="n">
         <v>22</v>
       </c>
-      <c r="Q369" t="n">
-        <v>0</v>
-      </c>
       <c r="R369" t="n">
         <v>0.4791209437375898</v>
       </c>
@@ -66773,9 +66440,6 @@
       <c r="O373" t="n">
         <v>25</v>
       </c>
-      <c r="Q373" t="n">
-        <v>0</v>
-      </c>
       <c r="R373" t="n">
         <v>0.4781808013086087</v>
       </c>
@@ -67317,9 +66981,6 @@
       <c r="O376" t="n">
         <v>29</v>
       </c>
-      <c r="Q376" t="n">
-        <v>0</v>
-      </c>
       <c r="R376" t="n">
         <v>0.6315685167450048</v>
       </c>
@@ -68009,9 +67670,6 @@
       <c r="O380" t="n">
         <v>38</v>
       </c>
-      <c r="Q380" t="n">
-        <v>0</v>
-      </c>
       <c r="R380" t="n">
         <v>0.7268348179890852</v>
       </c>
@@ -68553,9 +68211,6 @@
       <c r="O383" t="n">
         <v>16</v>
       </c>
-      <c r="Q383" t="n">
-        <v>0</v>
-      </c>
       <c r="R383" t="n">
         <v>0.3484515954455199</v>
       </c>
@@ -69245,9 +68900,6 @@
       <c r="O387" t="n">
         <v>25</v>
       </c>
-      <c r="Q387" t="n">
-        <v>0</v>
-      </c>
       <c r="R387" t="n">
         <v>0.4781808013086087</v>
       </c>
@@ -69789,9 +69441,6 @@
       <c r="O390" t="n">
         <v>20</v>
       </c>
-      <c r="Q390" t="n">
-        <v>0</v>
-      </c>
       <c r="R390" t="n">
         <v>0.4355644943068998</v>
       </c>
@@ -70481,9 +70130,6 @@
       <c r="O394" t="n">
         <v>23</v>
       </c>
-      <c r="Q394" t="n">
-        <v>0</v>
-      </c>
       <c r="R394" t="n">
         <v>0.43992633720392</v>
       </c>
@@ -71025,9 +70671,6 @@
       <c r="O397" t="n">
         <v>29</v>
       </c>
-      <c r="Q397" t="n">
-        <v>0</v>
-      </c>
       <c r="R397" t="n">
         <v>0.6315685167450048</v>
       </c>
@@ -71717,9 +71360,6 @@
       <c r="O401" t="n">
         <v>32</v>
       </c>
-      <c r="Q401" t="n">
-        <v>0</v>
-      </c>
       <c r="R401" t="n">
         <v>0.6120714256750192</v>
       </c>
@@ -72261,9 +71901,6 @@
       <c r="O404" t="n">
         <v>30</v>
       </c>
-      <c r="Q404" t="n">
-        <v>0</v>
-      </c>
       <c r="R404" t="n">
         <v>0.6533467414603498</v>
       </c>
@@ -72953,9 +72590,6 @@
       <c r="O408" t="n">
         <v>32</v>
       </c>
-      <c r="Q408" t="n">
-        <v>0</v>
-      </c>
       <c r="R408" t="n">
         <v>0.6120714256750192</v>
       </c>
@@ -73497,9 +73131,6 @@
       <c r="O411" t="n">
         <v>15</v>
       </c>
-      <c r="Q411" t="n">
-        <v>0</v>
-      </c>
       <c r="R411" t="n">
         <v>0.3266733707301749</v>
       </c>
@@ -74189,9 +73820,6 @@
       <c r="O415" t="n">
         <v>26</v>
       </c>
-      <c r="Q415" t="n">
-        <v>0</v>
-      </c>
       <c r="R415" t="n">
         <v>0.497308033360953</v>
       </c>
@@ -74732,9 +74360,6 @@
       </c>
       <c r="O418" t="n">
         <v>43</v>
-      </c>
-      <c r="Q418" t="n">
-        <v>0</v>
       </c>
       <c r="R418" t="n">
         <v>0.9364636627598346</v>
